--- a/04_試験/総合テスト/エビデンス.xlsx
+++ b/04_試験/総合テスト/エビデンス.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\04_試験\総合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5424E26-93D5-46B4-A4F3-2915EAABFEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931A6F82-F853-476A-976A-B997ACDC578C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9591B48A-FB26-4590-800B-40A993CA7CFF}"/>
   </bookViews>
@@ -97,183 +97,18 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>524189</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>114698</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848900F4-EA4A-4C51-B020-8377A9380814}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1704975" y="600075"/>
-          <a:ext cx="2248214" cy="2848373"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>340500</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>150000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>436433</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>83715</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDA1BA74-D5B6-4C7B-BE5A-ED7B18A3F058}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1712100" y="3721875"/>
-          <a:ext cx="4896533" cy="2791215"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>357150</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>138075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>538533</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>43244</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA46D705-340D-4CBC-B751-E40B24BD0137}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1728750" y="6805575"/>
-          <a:ext cx="2924583" cy="3000794"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -288,7 +123,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4162425" y="590550"/>
+          <a:off x="4143375" y="600075"/>
           <a:ext cx="2105025" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -323,7 +158,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>1) </a:t>
+            <a:t>2) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -347,16 +182,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -371,8 +206,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6867525" y="3724275"/>
-          <a:ext cx="2105025" cy="428625"/>
+          <a:off x="6848475" y="7715250"/>
+          <a:ext cx="2105025" cy="676275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -406,13 +241,71 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>2) </a:t>
+            <a:t>3.2) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>商品検索結果画面</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>遷移</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>後</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -420,23 +313,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="テキスト ボックス 9">
+        <xdr:cNvPr id="11" name="テキスト ボックス 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5648FB43-8227-4CE2-973E-0CA75663D971}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D5F0C29-7C3C-4582-94DA-5DB261D84B59}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -444,8 +337,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4914900" y="6810375"/>
-          <a:ext cx="2105025" cy="428625"/>
+          <a:off x="4286250" y="4657725"/>
+          <a:ext cx="2105025" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -479,16 +372,653 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>3) </a:t>
+            <a:t>3.1) </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>商品詳細表示画面</a:t>
+            <a:t>商品検索画面</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>遷移前</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="テキスト ボックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{570279F4-2B16-4F01-BC14-A387A7957666}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4876800" y="14582775"/>
+          <a:ext cx="2105025" cy="676275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>4.2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品詳細表示画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>遷移</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>後</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DA67DD8-910F-4C0E-96EE-BDC38E19D479}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6800850" y="11591925"/>
+          <a:ext cx="2105025" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>4.1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品検索結果画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>遷移前</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="テキスト ボックス 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47744357-188F-4E7D-AEAE-E8D8D6E40151}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4867275" y="18716625"/>
+          <a:ext cx="2105025" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>6.1) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>商品詳細表示画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>遷移前</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>476557</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28959</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14EF5C24-E45D-4429-928B-F8B09FD004DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1704975" y="609600"/>
+          <a:ext cx="2200582" cy="2753109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>330975</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>140475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>607526</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>74190</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{787C39FF-A583-4821-9006-03D728B3E541}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1702575" y="4664850"/>
+          <a:ext cx="2333951" cy="2791215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>338100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>395928</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>195604</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E11FCAFE-F4DF-4C3D-AAA0-10B24D1431C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1709700" y="7719975"/>
+          <a:ext cx="4858428" cy="2715004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>326175</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>59475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>469453</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>88453</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF382CA7-D824-4F18-91BE-B5525F9E0D0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1697775" y="14585100"/>
+          <a:ext cx="2886478" cy="2886478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>314250</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>142800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>505159</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>200357</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13091632-CF8E-4F75-B13A-1867E46A279E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1685850" y="18716550"/>
+          <a:ext cx="2934109" cy="2915057"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>328575</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>176175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>386403</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>33679</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5DA9583-E608-4D85-931C-28964F6B5B2F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1700175" y="11606175"/>
+          <a:ext cx="4858428" cy="2715004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
